--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2467-2083-CM25</t>
+          <t>4157-890-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9938.17</v>
+        <v>6267.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1431214-30-CM25</t>
+          <t>3904-1126-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18240.78</v>
+        <v>8091.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2471-2263-CM25</t>
+          <t>2467-2083-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12356.96</v>
+        <v>9938.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2471-2267-CM25</t>
+          <t>1431214-30-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>MUNICIPALIDAD DE QUILLÓN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23343.52</v>
+        <v>18240.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2471-2300-CM25</t>
+          <t>2471-2263-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12493.22</v>
+        <v>12356.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4594-1205-CM25</t>
+          <t>2471-2267-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12469.68</v>
+        <v>23343.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1070132-15-CM25</t>
+          <t>2471-2300-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>821.61</v>
+        <v>12493.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2471-2504-CM25</t>
+          <t>4594-1205-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>26657.7</v>
+        <v>12469.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3746-188-CM25</t>
+          <t>1070132-15-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4491.85</v>
+        <v>821.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3659-19-CM26</t>
+          <t>2471-2504-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18179.33</v>
+        <v>26657.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2467-4-CM26</t>
+          <t>3746-188-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>17776.22</v>
+        <v>4491.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2727-96-CM26</t>
+          <t>3659-19-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>967.47</v>
+        <v>18179.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2467-47-CM26</t>
+          <t>2467-4-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>13711.89</v>
+        <v>17776.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3659-120-CM26</t>
+          <t>2727-96-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3070.8</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>229-138-CM26</t>
+          <t>2467-47-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>16670.64</v>
+        <v>13711.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4364-91-CM26</t>
+          <t>3659-120-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1587.39</v>
+        <v>3070.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2467-186-CM26</t>
+          <t>229-138-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3981.15</v>
+        <v>16670.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1036569-48-CM26</t>
+          <t>4364-91-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>Ilustre Municipalidad de Quillon - Educación</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6210.94</v>
+        <v>1587.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1233616-690-CM26</t>
+          <t>2467-186-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1582.01</v>
+        <v>3981.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1233616-691-CM26</t>
+          <t>1036569-48-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Gobierno Regional de Ñuble</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>542.64</v>
+        <v>6210.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2705-405-CM26</t>
+          <t>1233616-690-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12431.13</v>
+        <v>1582.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2467-296-CM26</t>
+          <t>1233616-691-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3885.35</v>
+        <v>542.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3904-337-CM26</t>
+          <t>2705-405-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10692.44</v>
+        <v>12431.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3706-183-CM26</t>
+          <t>2467-296-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4199.11</v>
+        <v>3885.35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3497-232-CM26</t>
+          <t>3904-337-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4546.1</v>
+        <v>10692.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2467-451-CM26</t>
+          <t>3706-183-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>726.1900000000001</v>
+        <v>4199.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4364-238-CM26</t>
+          <t>3497-232-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6770.86</v>
+        <v>4546.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1233616-955-CM26</t>
+          <t>2467-451-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12428.16</v>
+        <v>726.1900000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1233616-956-CM26</t>
+          <t>4364-238-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Ilustre Municipalidad de Quillon - Educación</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6045.1</v>
+        <v>6770.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1233616-958-CM26</t>
+          <t>1233616-955-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9346.09</v>
+        <v>12428.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4174-189-CM26</t>
+          <t>1233616-956-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1304.24</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2727-353-CM26</t>
+          <t>1233616-958-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5264.46</v>
+        <v>9346.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1233616-957-CM26</t>
+          <t>4174-189-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10433.92</v>
+        <v>1304.24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2467-473-CM26</t>
+          <t>2727-353-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2444.26</v>
+        <v>5264.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4174-198-CM26</t>
+          <t>1233616-957-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2698.92</v>
+        <v>10433.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3588-214-CM26</t>
+          <t>2467-473-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12941.25</v>
+        <v>2444.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3449-65-CM26</t>
+          <t>4174-198-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7485.22</v>
+        <v>2698.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4364-279-CM26</t>
+          <t>3588-214-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5348.05</v>
+        <v>12941.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3747-153-CM26</t>
+          <t>3449-65-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>969.61</v>
+        <v>7485.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5615-360-CM26</t>
+          <t>4364-279-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de Quillon - Educación</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5664.32</v>
+        <v>5348.05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1393-296-CM26</t>
+          <t>5615-360-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I.Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3286.66</v>
+        <v>5664.32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2467-696-CM26</t>
+          <t>3747-153-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>855.61</v>
+        <v>969.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1393-312-CM26</t>
+          <t>1393-296-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5052.7</v>
+        <v>3286.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4252-164-CM26</t>
+          <t>2467-696-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4040.05</v>
+        <v>855.61</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4252-165-CM26</t>
+          <t>1393-312-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4073.51</v>
+        <v>5052.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1393-328-CM26</t>
+          <t>4252-164-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1473.22</v>
+        <v>4040.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2467-791-CM26</t>
+          <t>4252-165-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5656.07</v>
+        <v>4073.51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057898-82-CM26</t>
+          <t>1393-328-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>61013.68</v>
+        <v>1473.22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3659-584-CM26</t>
+          <t>2467-791-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>13036.95</v>
+        <v>5656.07</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2727-578-CM26</t>
+          <t>1057898-82-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3845.13</v>
+        <v>61013.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2467-870-CM26</t>
+          <t>3659-584-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,6 +3619,128 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
+        <v>13036.95</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2727-578-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>3845.13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2467-870-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
         <v>968.65</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4157-890-CM25</t>
+          <t>3588-8-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6267.02</v>
+        <v>5626.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3904-1126-CM25</t>
+          <t>4121-8-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8091.17</v>
+        <v>4968.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2467-2083-CM25</t>
+          <t>4121-9-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9938.17</v>
+        <v>6898.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1431214-30-CM25</t>
+          <t>2467-53-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>18240.78</v>
+        <v>18593.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2471-2263-CM25</t>
+          <t>3673-30-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12356.96</v>
+        <v>7794.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2471-2267-CM25</t>
+          <t>501-22-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>23343.52</v>
+        <v>2561.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2471-2300-CM25</t>
+          <t>3588-95-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12493.22</v>
+        <v>6830.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4594-1205-CM25</t>
+          <t>3659-122-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12469.68</v>
+        <v>9222.379999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1070132-15-CM25</t>
+          <t>4594-113-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>821.61</v>
+        <v>10248.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2471-2504-CM25</t>
+          <t>501-55-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26657.7</v>
+        <v>11005.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3746-188-CM25</t>
+          <t>3659-212-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4491.85</v>
+        <v>7833.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3659-19-CM26</t>
+          <t>3594-247-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.200-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,43 +1240,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18179.33</v>
+        <v>2282.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2467-4-CM26</t>
+          <t>3594-248-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.200-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17776.22</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2727-96-CM26</t>
+          <t>4364-115-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>967.47</v>
+        <v>3105.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2467-47-CM26</t>
+          <t>3904-379-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13711.89</v>
+        <v>5669.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3659-120-CM26</t>
+          <t>3785-121-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,28 +1484,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3070.8</v>
+        <v>22359.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>229-138-CM26</t>
+          <t>2467-674-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>16670.64</v>
+        <v>14271.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4364-91-CM26</t>
+          <t>2724-893-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,28 +1606,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1587.39</v>
+        <v>3725.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2467-186-CM26</t>
+          <t>229-240-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3981.15</v>
+        <v>18957.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1036569-48-CM26</t>
+          <t>2724-923-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,43 +1728,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6210.94</v>
+        <v>4469.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1233616-690-CM26</t>
+          <t>2129-115-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1582.01</v>
+        <v>7264.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1233616-691-CM26</t>
+          <t>2727-337-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,28 +1850,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>542.64</v>
+        <v>16406.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2705-405-CM26</t>
+          <t>2467-913-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,28 +1911,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>12431.13</v>
+        <v>21842.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2467-296-CM26</t>
+          <t>3673-223-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,28 +1972,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3885.35</v>
+        <v>12754.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3904-337-CM26</t>
+          <t>3673-231-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,43 +2033,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10692.44</v>
+        <v>4750.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3706-183-CM26</t>
+          <t>2471-1075-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,43 +2094,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4199.11</v>
+        <v>7459.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3497-232-CM26</t>
+          <t>3589-962-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,28 +2155,28 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4546.1</v>
+        <v>12181.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2467-451-CM26</t>
+          <t>4594-526-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,28 +2216,28 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>726.1900000000001</v>
+        <v>8497.530000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4364-238-CM26</t>
+          <t>4364-277-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,43 +2277,43 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6770.86</v>
+        <v>10918.73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1233616-955-CM26</t>
+          <t>3449-91-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,43 +2338,43 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12428.16</v>
+        <v>9878.860000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1233616-956-CM26</t>
+          <t>3449-92-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,28 +2399,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6045.1</v>
+        <v>16877.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1233616-958-CM26</t>
+          <t>3747-236-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,43 +2460,43 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>9346.09</v>
+        <v>2427.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4174-189-CM26</t>
+          <t>4157-890-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,28 +2521,28 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1304.24</v>
+        <v>6267.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2727-353-CM26</t>
+          <t>2471-1327-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,43 +2582,43 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5264.46</v>
+        <v>27786.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1233616-957-CM26</t>
+          <t>3904-1126-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,28 +2643,28 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10433.92</v>
+        <v>8091.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2467-473-CM26</t>
+          <t>501-330-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2444.26</v>
+        <v>8056.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4174-198-CM26</t>
+          <t>3871-247-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>72.632.100-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,28 +2765,28 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2698.92</v>
+        <v>3659.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3588-214-CM26</t>
+          <t>3871-248-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>72.632.100-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,28 +2826,28 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12941.25</v>
+        <v>4339.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3449-65-CM26</t>
+          <t>2467-1756-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,43 +2887,43 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7485.22</v>
+        <v>3836.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4364-279-CM26</t>
+          <t>2727-856-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,28 +2948,28 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5348.05</v>
+        <v>5135.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5615-360-CM26</t>
+          <t>2467-1797-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,43 +3009,43 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5664.32</v>
+        <v>2391.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3747-153-CM26</t>
+          <t>1233616-8051-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,28 +3070,28 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>969.61</v>
+        <v>62405.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1393-296-CM26</t>
+          <t>2129-290-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,28 +3131,28 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3286.66</v>
+        <v>12723.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2467-696-CM26</t>
+          <t>3785-342-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,28 +3192,28 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>855.61</v>
+        <v>6758.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1393-312-CM26</t>
+          <t>2467-2083-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,28 +3253,28 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5052.7</v>
+        <v>9938.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4252-164-CM26</t>
+          <t>1431214-30-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>MUNICIPALIDAD DE QUILLÓN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,43 +3314,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4040.05</v>
+        <v>18240.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4252-165-CM26</t>
+          <t>2471-2300-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,43 +3375,43 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4073.51</v>
+        <v>12493.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1393-328-CM26</t>
+          <t>2471-2267-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,33 +3436,33 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1473.22</v>
+        <v>23343.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2467-791-CM26</t>
+          <t>2471-2263-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5656.07</v>
+        <v>12356.96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057898-82-CM26</t>
+          <t>4594-1205-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>61013.68</v>
+        <v>12469.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3659-584-CM26</t>
+          <t>1070132-15-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>13036.95</v>
+        <v>821.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2727-578-CM26</t>
+          <t>2471-2504-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3845.13</v>
+        <v>26657.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2467-870-CM26</t>
+          <t>3746-188-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,7 +3741,2996 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
+        <v>4491.85</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3659-19-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>18179.33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2467-4-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>17776.22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2727-96-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>967.47</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2467-47-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>13711.89</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3659-120-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>3070.8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>229-138-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.141.100-1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>16670.64</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4364-91-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.141.401-9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quillon - Educación</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1587.39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2467-186-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>3981.15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1036569-48-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gobierno Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>6210.94</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1233616-690-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>1582.01</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1233616-691-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>542.64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2705-405-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>12431.13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2467-296-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>3885.35</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3904-337-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>10692.44</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3706-183-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.141.300-4</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>4199.11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3497-232-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.140.400-5</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>4546.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2467-451-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>726.1900000000001</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4364-238-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.141.401-9</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quillon - Educación</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>6770.86</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1233616-955-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>12428.16</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1233616-956-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>6045.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1233616-958-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>9346.09</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4174-189-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1304.24</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2727-353-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>5264.46</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1233616-957-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>10433.92</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2467-473-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2444.26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4174-198-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>2698.92</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3588-214-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.141.500-7</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>12941.25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3449-65-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.140.400-5</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>7485.22</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4364-279-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.141.401-9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quillon - Educación</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>5348.05</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5615-360-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.141.700-K</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I.Municipalidad de El Carmen</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>5664.32</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3747-153-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.141.300-4</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>969.61</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1393-296-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>3286.66</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2467-696-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>855.61</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1393-312-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>5052.7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4252-164-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.140.700-4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>4040.05</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4252-165-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>69.140.700-4</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>4073.51</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1393-328-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1473.22</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2467-791-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>5656.07</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1057898-82-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.607.000-2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>61013.68</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3659-584-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>13036.95</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2727-578-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>3845.13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2467-870-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
         <v>968.65</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2727-682-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>2010.03</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2727-684-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>760.41</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1069417-916-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>1011.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3659-720-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>6832.59</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2727-733-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>15820.1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2467-1019-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>1472.74</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4174-424-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quirihue</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>791</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3904-379-CM25</t>
+          <t>2467-674-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5669.31</v>
+        <v>14271.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3785-121-CM25</t>
+          <t>3904-379-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>22359.27</v>
+        <v>5669.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2467-674-CM25</t>
+          <t>3785-121-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14271.61</v>
+        <v>22359.27</v>
       </c>
     </row>
     <row r="19">
@@ -2039,7 +2039,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2471-1075-CM25</t>
+          <t>3589-962-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7459.87</v>
+        <v>12181.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3589-962-CM25</t>
+          <t>2471-1075-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>12181.98</v>
+        <v>7459.87</v>
       </c>
     </row>
     <row r="29">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3449-91-CM25</t>
+          <t>3449-92-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9878.860000000001</v>
+        <v>16877.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3449-92-CM25</t>
+          <t>3449-91-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>16877.75</v>
+        <v>9878.860000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2710,7 +2710,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3871-247-CM25</t>
+          <t>3871-248-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3659.25</v>
+        <v>4339.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3871-248-CM25</t>
+          <t>3871-247-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4339.1</v>
+        <v>3659.25</v>
       </c>
     </row>
     <row r="40">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2471-2300-CM25</t>
+          <t>2471-2267-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>12493.22</v>
+        <v>23343.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2471-2267-CM25</t>
+          <t>2471-2300-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>23343.52</v>
+        <v>12493.22</v>
       </c>
     </row>
     <row r="50">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2471-2504-CM25</t>
+          <t>3746-188-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>26657.7</v>
+        <v>4491.85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3746-188-CM25</t>
+          <t>2471-2504-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4491.85</v>
+        <v>26657.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3659-19-CM26</t>
+          <t>1395824-1-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>65.103.712-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ASOCIACION DE MUNICIPALIDADES DEL VALLE DEL ITATA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>18179.33</v>
+        <v>759.6799999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2467-4-CM26</t>
+          <t>3659-19-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>17776.22</v>
+        <v>18179.33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2727-96-CM26</t>
+          <t>2467-4-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>967.47</v>
+        <v>17776.22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2467-47-CM26</t>
+          <t>2727-96-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>13711.89</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3659-120-CM26</t>
+          <t>2467-47-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3070.8</v>
+        <v>13711.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>229-138-CM26</t>
+          <t>3659-120-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>16670.64</v>
+        <v>3070.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4364-91-CM26</t>
+          <t>229-138-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1587.39</v>
+        <v>16670.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2467-186-CM26</t>
+          <t>4364-91-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3981.15</v>
+        <v>1587.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1036569-48-CM26</t>
+          <t>2467-186-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6210.94</v>
+        <v>3981.15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1233616-690-CM26</t>
+          <t>1036569-48-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1582.01</v>
+        <v>6210.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1233616-691-CM26</t>
+          <t>1233616-690-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>542.64</v>
+        <v>1582.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2705-405-CM26</t>
+          <t>1233616-691-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>12431.13</v>
+        <v>542.64</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2467-296-CM26</t>
+          <t>2705-405-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3885.35</v>
+        <v>12431.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3904-337-CM26</t>
+          <t>2467-296-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>10692.44</v>
+        <v>3885.35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3706-183-CM26</t>
+          <t>3904-337-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4199.11</v>
+        <v>10692.44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3497-232-CM26</t>
+          <t>3706-183-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4546.1</v>
+        <v>4199.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2467-451-CM26</t>
+          <t>3497-232-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>726.1900000000001</v>
+        <v>4546.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4364-238-CM26</t>
+          <t>2467-451-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6770.86</v>
+        <v>726.1900000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1233616-955-CM26</t>
+          <t>4364-238-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>12428.16</v>
+        <v>6770.86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1233616-956-CM26</t>
+          <t>1233616-955-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6045.1</v>
+        <v>12428.16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1233616-958-CM26</t>
+          <t>1233616-956-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>9346.09</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4174-189-CM26</t>
+          <t>1233616-958-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1304.24</v>
+        <v>9346.09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2727-353-CM26</t>
+          <t>4174-189-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5264.46</v>
+        <v>1304.24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1233616-957-CM26</t>
+          <t>2727-353-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>10433.92</v>
+        <v>5264.46</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2467-473-CM26</t>
+          <t>1233616-957-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2444.26</v>
+        <v>10433.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4174-198-CM26</t>
+          <t>2467-473-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2698.92</v>
+        <v>2444.26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3588-214-CM26</t>
+          <t>4174-198-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>12941.25</v>
+        <v>2698.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3449-65-CM26</t>
+          <t>3588-214-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7485.22</v>
+        <v>12941.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4364-279-CM26</t>
+          <t>3449-65-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5348.05</v>
+        <v>7485.22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5615-360-CM26</t>
+          <t>4364-279-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5664.32</v>
+        <v>5348.05</v>
       </c>
     </row>
     <row r="85">
@@ -5638,7 +5638,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1393-296-CM26</t>
+          <t>5615-360-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3286.66</v>
+        <v>5664.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2467-696-CM26</t>
+          <t>1393-296-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>855.61</v>
+        <v>3286.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1393-312-CM26</t>
+          <t>2467-696-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>5052.7</v>
+        <v>855.61</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4252-164-CM26</t>
+          <t>1393-312-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4040.05</v>
+        <v>5052.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4252-165-CM26</t>
+          <t>4252-164-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4073.51</v>
+        <v>4040.05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1393-328-CM26</t>
+          <t>4252-165-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1473.22</v>
+        <v>4073.51</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2467-791-CM26</t>
+          <t>1393-328-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5656.07</v>
+        <v>1473.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057898-82-CM26</t>
+          <t>2467-791-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>61013.68</v>
+        <v>5656.07</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3659-584-CM26</t>
+          <t>1057898-82-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>13036.95</v>
+        <v>61013.68</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2727-578-CM26</t>
+          <t>3659-584-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3845.13</v>
+        <v>13036.95</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2467-870-CM26</t>
+          <t>2727-578-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>968.65</v>
+        <v>3845.13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2727-682-CM26</t>
+          <t>2467-870-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,27 +6319,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2010.03</v>
+        <v>968.65</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2727-684-CM26</t>
+          <t>2727-682-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>760.41</v>
+        <v>2010.03</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1069417-916-CM26</t>
+          <t>2727-684-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1011.5</v>
+        <v>760.41</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3659-720-CM26</t>
+          <t>1069417-916-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6832.59</v>
+        <v>1011.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2727-733-CM26</t>
+          <t>3659-720-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>15820.1</v>
+        <v>6832.59</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2467-1019-CM26</t>
+          <t>2727-733-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,22 +6629,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1472.74</v>
+        <v>15820.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4174-424-CM26</t>
+          <t>2467-1019-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,7 +6730,617 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
+        <v>1472.74</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4174-424-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quirihue</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
         <v>791</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>501-333-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.150.300-3</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Ranquil</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>4750.13</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1047296-101-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>62.000.460-K</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Delegación Presidencial Provincial de Itata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>3148.74</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1043046-98-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>62.000.450-2</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>3154.81</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1052836-117-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>62.000.470-7</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PUNILLA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>3154.81</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>4174-472-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quirihue</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>1089.43</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1036569-141-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>10562.68</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3674-564-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1938.51</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3674-571-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>9772.09</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>3674-597-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>277.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -684,7 +684,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1712,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2155,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2220,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2285,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2480,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2984,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3049,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3179,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3427,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3553,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3618,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3683,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3809,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3874,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3939,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4004,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4130,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4195,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4260,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4325,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4390,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4516,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4581,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4829,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4894,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4959,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5024,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5089,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5154,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5219,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5284,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5593,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5658,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5784,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5910,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6036,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6223,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6288,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6414,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6540,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6605,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6670,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6796,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6922,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6987,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7052,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7117,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7243,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7308,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7434,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7499,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7564,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7629,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1217,7 +1217,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3594-247-CM25</t>
+          <t>3594-248-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1257,32 +1257,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2282.07</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3594-248-CM25</t>
+          <t>3594-247-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1322,22 +1318,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2491</v>
+        <v>2282.07</v>
       </c>
     </row>
     <row r="15">
@@ -2367,7 +2367,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3449-92-CM25</t>
+          <t>3449-91-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16877.75</v>
+        <v>9878.860000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3449-91-CM25</t>
+          <t>3449-92-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9878.860000000001</v>
+        <v>16877.75</v>
       </c>
     </row>
     <row r="33">
@@ -2814,7 +2814,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3871-248-CM25</t>
+          <t>3871-247-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2869,13 +2869,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4339.1</v>
+        <v>3659.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3871-247-CM25</t>
+          <t>3871-248-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3659.25</v>
+        <v>4339.1</v>
       </c>
     </row>
     <row r="40">
@@ -4533,7 +4533,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1233616-690-CM26</t>
+          <t>2705-405-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4553,17 +4553,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4573,26 +4573,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1582.01</v>
+        <v>12431.13</v>
       </c>
     </row>
     <row r="66">
@@ -4659,7 +4655,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2705-405-CM26</t>
+          <t>1233616-690-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4679,17 +4675,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4699,22 +4695,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>12431.13</v>
+        <v>1582.01</v>
       </c>
     </row>
     <row r="68">
@@ -5106,7 +5106,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1233616-955-CM26</t>
+          <t>1233616-956-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>12428.16</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1233616-956-CM26</t>
+          <t>1233616-955-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6045.1</v>
+        <v>12428.16</v>
       </c>
     </row>
     <row r="76">
@@ -5484,7 +5484,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2467-473-CM26</t>
+          <t>4174-198-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5524,28 +5524,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2444.26</v>
+        <v>2698.92</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4174-198-CM26</t>
+          <t>2467-473-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5570,12 +5574,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5585,26 +5589,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2698.92</v>
+        <v>2444.26</v>
       </c>
     </row>
     <row r="82">
@@ -7069,7 +7069,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>501-333-CM26</t>
+          <t>4174-472-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7109,32 +7109,28 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>4750.13</v>
+        <v>1089.43</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1047296-101-CM26</t>
+          <t>1052836-117-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7154,17 +7150,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.460-K</t>
+          <t>62.000.470-7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Delegación Presidencial Provincial de Itata</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PUNILLA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7174,28 +7170,32 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3148.74</v>
+        <v>3154.81</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1043046-98-CM26</t>
+          <t>1047296-101-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7215,17 +7215,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.000.450-2</t>
+          <t>62.000.460-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+          <t>Delegación Presidencial Provincial de Itata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7235,32 +7235,28 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3154.81</v>
+        <v>3148.74</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1052836-117-CM26</t>
+          <t>1043046-98-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7280,17 +7276,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.000.470-7</t>
+          <t>62.000.450-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PUNILLA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7325,7 +7321,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4174-472-CM26</t>
+          <t>3674-564-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7340,7 +7336,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7350,12 +7346,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7365,22 +7361,26 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1089.43</v>
+        <v>1938.51</v>
       </c>
     </row>
     <row r="110">
@@ -7451,7 +7451,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3674-564-CM26</t>
+          <t>3674-571-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7510,13 +7510,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1938.51</v>
+        <v>9772.09</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3674-571-CM26</t>
+          <t>3674-597-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7575,13 +7575,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>9772.09</v>
+        <v>277.59</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3674-597-CM26</t>
+          <t>1375761-1572-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7591,56 +7591,434 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.981.330-8</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>IMPORTADORA HEVIA SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>192680.04</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3674-603-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>69.266.500-7</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>BOOKCOMPUTER</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>277.59</v>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>18540.2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1233616-1864-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>1632.68</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1233616-1863-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>20170.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1233616-1862-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>50249.54</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4364-543-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.141.401-9</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>2948.11</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3904-1150-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>5027.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4533,7 +4533,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2705-405-CM26</t>
+          <t>1233616-691-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4553,17 +4553,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4588,13 +4588,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>12431.13</v>
+        <v>542.64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1233616-691-CM26</t>
+          <t>1233616-690-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4634,28 +4634,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>542.64</v>
+        <v>1582.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1233616-690-CM26</t>
+          <t>2705-405-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4675,17 +4679,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4695,26 +4699,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1582.01</v>
+        <v>12431.13</v>
       </c>
     </row>
     <row r="68">
@@ -5106,7 +5106,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1233616-956-CM26</t>
+          <t>1233616-955-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6045.1</v>
+        <v>12428.16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1233616-955-CM26</t>
+          <t>1233616-956-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5230,13 +5230,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>12428.16</v>
+        <v>6045.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1233616-958-CM26</t>
+          <t>4174-189-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5276,32 +5276,28 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>9346.09</v>
+        <v>1304.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4174-189-CM26</t>
+          <t>1233616-958-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5326,12 +5322,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5341,28 +5337,32 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1304.24</v>
+        <v>9346.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2727-353-CM26</t>
+          <t>1233616-957-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5264.46</v>
+        <v>10433.92</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1233616-957-CM26</t>
+          <t>2727-353-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10433.92</v>
+        <v>5264.46</v>
       </c>
     </row>
     <row r="80">
@@ -5801,7 +5801,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3747-153-CM26</t>
+          <t>5615-360-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5841,28 +5841,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>969.61</v>
+        <v>5664.32</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5615-360-CM26</t>
+          <t>3747-153-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5887,12 +5891,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5902,26 +5906,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5664.32</v>
+        <v>969.61</v>
       </c>
     </row>
     <row r="87">
@@ -7195,7 +7195,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1047296-101-CM26</t>
+          <t>1043046-98-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.000.460-K</t>
+          <t>62.000.450-2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Delegación Presidencial Provincial de Itata</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7235,28 +7235,32 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3148.74</v>
+        <v>3154.81</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1043046-98-CM26</t>
+          <t>1047296-101-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7281,12 +7285,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.000.450-2</t>
+          <t>62.000.460-K</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+          <t>Delegación Presidencial Provincial de Itata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7296,26 +7300,22 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3154.81</v>
+        <v>3148.74</v>
       </c>
     </row>
     <row r="109">
@@ -7837,7 +7837,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1233616-1862-CM26</t>
+          <t>4364-543-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7857,17 +7857,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7877,32 +7877,28 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>50249.54</v>
+        <v>2948.11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4364-543-CM26</t>
+          <t>1233616-1862-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7922,17 +7918,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7942,22 +7938,26 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2948.11</v>
+        <v>50249.54</v>
       </c>
     </row>
     <row r="119">
@@ -8019,6 +8019,67 @@
       </c>
       <c r="M119" s="2" t="n">
         <v>5027.69</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1070132-11-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>61.301.000-9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>215.03</v>
       </c>
     </row>
   </sheetData>
